--- a/volunteer_forms/014_new_volunteer_registration_form--volunteer_forms.xlsx
+++ b/volunteer_forms/014_new_volunteer_registration_form--volunteer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1568,34 +1568,34 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>new_vols_volunteer_availability_choices</t>
+          <t>new_vols_volunteer_shift_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>available</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>new_vols_volunteer_availability_choices</t>
+          <t>new_vols_volunteer_shift_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>available</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>morning</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1624,46 +1624,46 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>afternoon</t>
+          <t>weekend</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Afternoon</t>
+          <t>Weekend</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>new_vols_volunteer_shift_choices</t>
+          <t>new_vols_volunteer_flexible_time_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>evening</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>new_vols_volunteer_shift_choices</t>
+          <t>new_vols_volunteer_flexible_time_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>weekend</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Weekend</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>morning</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1692,46 +1692,46 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>afternoon</t>
+          <t>weekend</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Afternoon</t>
+          <t>Weekend</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>new_vols_volunteer_flexible_time_choices</t>
+          <t>new_vols_volunteer_volunteer_type_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>evening</t>
+          <t>type1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Type1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>new_vols_volunteer_flexible_time_choices</t>
+          <t>new_vols_volunteer_volunteer_type_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>weekend</t>
+          <t>type2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Weekend</t>
+          <t>Type2</t>
         </is>
       </c>
     </row>
@@ -1743,53 +1743,53 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>type1</t>
+          <t>type3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Type1</t>
+          <t>Type3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>new_vols_volunteer_volunteer_type_choices</t>
+          <t>new_vols_volunteer_volunteer_hours_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>type2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Type2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>new_vols_volunteer_volunteer_type_choices</t>
+          <t>new_vols_volunteer_volunteer_hours_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>type3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Type3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>new_vols_volunteer_volunteer_hours_choices</t>
+          <t>new_vols_volunteer_shift_hours_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1806,7 +1806,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>new_vols_volunteer_volunteer_hours_choices</t>
+          <t>new_vols_volunteer_shift_hours_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1823,7 +1823,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>new_vols_volunteer_shift_hours_choices</t>
+          <t>new_vols_volunteer_terminology_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1840,7 +1840,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>new_vols_volunteer_shift_hours_choices</t>
+          <t>new_vols_volunteer_terminology_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1849,40 +1849,6 @@
         </is>
       </c>
       <c r="C44" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>new_vols_volunteer_terminology_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>new_vols_volunteer_terminology_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
         <is>
           <t>No</t>
         </is>
